--- a/data/trans_orig/KIDMED_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/KIDMED_R-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Escala de adherencia a la dieta mediterránea (Kidmed) en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Escala de adherencia a la dieta mediterránea (Kidmed) en 2023 (tasa de respuesta: 96,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -720,107 +720,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>31968</t>
+          <t>32500</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22823</t>
+          <t>22516</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40955</t>
+          <t>40880</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>22925</t>
+          <t>24088</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16482</t>
+          <t>16739</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30756</t>
+          <t>31223</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>54893</t>
+          <t>56588</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43944</t>
+          <t>45187</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66995</t>
+          <t>68384</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,84%</t>
         </is>
       </c>
     </row>
@@ -833,107 +833,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>39432</t>
+          <t>38900</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30445</t>
+          <t>30520</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48577</t>
+          <t>48884</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>49997</t>
+          <t>48834</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42375</t>
+          <t>41740</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56961</t>
+          <t>56447</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>111</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>89429</t>
+          <t>87734</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>77876</t>
+          <t>76122</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>101168</t>
+          <t>99863</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>68,4%</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6979</t>
+          <t>5586</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6152</t>
+          <t>6792</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -1176,107 +1176,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>59</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>40301</t>
+          <t>40717</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21948</t>
+          <t>17688</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54518</t>
+          <t>55505</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>45926</t>
+          <t>47147</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36045</t>
+          <t>36473</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59599</t>
+          <t>59265</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>120</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>86227</t>
+          <t>87864</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>57661</t>
+          <t>61602</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>103481</t>
+          <t>105634</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,91%</t>
         </is>
       </c>
     </row>
@@ -1289,107 +1289,107 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>81415</t>
+          <t>80999</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66296</t>
+          <t>65251</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>101531</t>
+          <t>106990</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>69272</t>
+          <t>68051</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>56465</t>
+          <t>56480</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>81386</t>
+          <t>80770</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>152</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>150686</t>
+          <t>149049</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>132491</t>
+          <t>129350</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>185328</t>
+          <t>179931</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>71,38%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8313</t>
+          <t>9830</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6262</t>
+          <t>5980</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19079</t>
+          <t>18683</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8690</t>
+          <t>9031</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23578</t>
+          <t>24078</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21730</t>
+          <t>21719</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33382</t>
+          <t>33704</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>37824</t>
+          <t>38099</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>51146</t>
+          <t>49850</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>63376</t>
+          <t>63232</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>80011</t>
+          <t>80980</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>67,38%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21416</t>
+          <t>21252</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33228</t>
+          <t>33142</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>13902</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25775</t>
+          <t>25679</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38917</t>
+          <t>37817</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55696</t>
+          <t>55615</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,27%</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2699</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>4728</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -2088,107 +2088,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>56</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>39476</t>
+          <t>41075</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32322</t>
+          <t>33700</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46650</t>
+          <t>48181</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>37673</t>
+          <t>39123</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20226</t>
+          <t>21894</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48604</t>
+          <t>50403</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>93</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>77149</t>
+          <t>80197</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>56827</t>
+          <t>58418</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>90118</t>
+          <t>92660</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>63,88%</t>
         </is>
       </c>
     </row>
@@ -2201,107 +2201,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>26003</t>
+          <t>24405</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19206</t>
+          <t>17835</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32970</t>
+          <t>31898</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>35697</t>
+          <t>34246</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24442</t>
+          <t>22624</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53525</t>
+          <t>51330</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>56</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>61700</t>
+          <t>58651</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>48124</t>
+          <t>46118</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>83398</t>
+          <t>82320</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>56,75%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>1569</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9004</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6774</t>
+          <t>7137</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2592</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12092</t>
+          <t>12975</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30553</t>
+          <t>30446</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33892</t>
+          <t>33887</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>37562</t>
+          <t>37566</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>70365</t>
+          <t>70162</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>74352</t>
+          <t>74344</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>313</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3647</t>
+          <t>3754</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3157</t>
+          <t>3153</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>575</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4554</t>
+          <t>4757</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10721</t>
+          <t>11312</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>20511</t>
+          <t>21477</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21329</t>
+          <t>21165</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>33172</t>
+          <t>33640</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>35842</t>
+          <t>35698</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>51765</t>
+          <t>51146</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,15%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21733</t>
+          <t>21205</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>31820</t>
+          <t>31203</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19701</t>
+          <t>19803</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31568</t>
+          <t>31894</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>43808</t>
+          <t>44347</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>59856</t>
+          <t>59847</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>61,02%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>535</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4853</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>3635</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>944</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5855</t>
+          <t>5768</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -3456,107 +3456,107 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>126</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>87209</t>
+          <t>87614</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>76744</t>
+          <t>77909</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>96360</t>
+          <t>96820</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>116</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>100347</t>
+          <t>101392</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>83735</t>
+          <t>85218</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>112523</t>
+          <t>113196</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>242</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>187556</t>
+          <t>189006</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>170636</t>
+          <t>171864</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>204532</t>
+          <t>203206</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>72,9%</t>
         </is>
       </c>
     </row>
@@ -3569,107 +3569,107 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>31463</t>
+          <t>31058</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>23028</t>
+          <t>23207</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>42027</t>
+          <t>41121</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>47153</t>
+          <t>46108</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>36098</t>
+          <t>35308</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>64715</t>
+          <t>61975</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>93</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>78616</t>
+          <t>77166</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>63450</t>
+          <t>63425</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>95395</t>
+          <t>95593</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,29%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2205</t>
+          <t>2142</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10204</t>
+          <t>10050</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>14982</t>
+          <t>15148</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7190</t>
+          <t>7115</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>20394</t>
+          <t>20674</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>108187</t>
+          <t>108703</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>120741</t>
+          <t>120863</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>134801</t>
+          <t>135254</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>146850</t>
+          <t>147159</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>248801</t>
+          <t>248827</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>265613</t>
+          <t>265822</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,99%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>7158</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>19243</t>
+          <t>19065</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>6854</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>18823</t>
+          <t>18119</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>16300</t>
+          <t>15693</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>33009</t>
+          <t>32440</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4850</t>
+          <t>4398</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2588</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -4368,107 +4368,107 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>585</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>391062</t>
+          <t>394014</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>338588</t>
+          <t>342979</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>418124</t>
+          <t>421661</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>613</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>461237</t>
+          <t>466116</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>428847</t>
+          <t>435981</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>487817</t>
+          <t>495052</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>852300</t>
+          <t>860130</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>787861</t>
+          <t>796725</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>891020</t>
+          <t>899449</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>64,34%</t>
         </is>
       </c>
     </row>
@@ -4481,107 +4481,107 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>306</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>245518</t>
+          <t>242566</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>219739</t>
+          <t>214177</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>302666</t>
+          <t>294628</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>297</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>258966</t>
+          <t>254087</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>232911</t>
+          <t>224987</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>290726</t>
+          <t>285754</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>603</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>504483</t>
+          <t>496653</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>466861</t>
+          <t>457445</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>573183</t>
+          <t>565634</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,46%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>10773</t>
+          <t>11175</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>24120</t>
+          <t>24904</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>16643</t>
+          <t>16282</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>36060</t>
+          <t>35530</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>30727</t>
+          <t>30492</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>56070</t>
+          <t>54260</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/KIDMED_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/KIDMED_R-Provincia-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Escala de adherencia a la dieta mediterránea (Kidmed) en 2023 (tasa de respuesta: 96,61%)</t>
+          <t>Menores según tipo de adherencia a la dieta mediterránea (Kidmed) en 2023 (tasa de respuesta: 96,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20300</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14631</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>26504</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>33,69%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>24,28%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>43,98%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>32500</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>22516</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>40880</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>45,52%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>31,53%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>57,25%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>24088</t>
+          <t>24174</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16739</t>
+          <t>18751</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31223</t>
+          <t>29665</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>56588</t>
+          <t>44474</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45187</t>
+          <t>36715</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68384</t>
+          <t>52706</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>45,76%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>38913</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>32628</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>44587</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>64,57%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>54,14%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>73,99%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>38900</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>30520</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>48884</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>54,48%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>42,75%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>68,47%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>48834</t>
+          <t>30748</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41740</t>
+          <t>25257</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56447</t>
+          <t>36171</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>87734</t>
+          <t>69662</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>76122</t>
+          <t>61274</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>99863</t>
+          <t>77632</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>67,4%</t>
         </is>
       </c>
     </row>
@@ -946,107 +946,107 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1050</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3883</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>6,44%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1685</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>1050</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>5586</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>3546</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>7,49%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>1685</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>6792</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -1059,57 +1059,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>42013</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>32402</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>53339</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>36,55%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>28,19%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>46,4%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>40717</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>17688</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>55505</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>32,41%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>14,08%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>44,17%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>47147</t>
+          <t>40313</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36473</t>
+          <t>31721</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59265</t>
+          <t>48448</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>87864</t>
+          <t>82326</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>61602</t>
+          <t>69539</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>105634</t>
+          <t>96328</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>44,95%</t>
         </is>
       </c>
     </row>
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>62822</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>52376</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>73376</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>54,65%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>45,56%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>63,83%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>80999</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>65251</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>106990</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>64,46%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>51,93%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>85,15%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>68051</t>
+          <t>55058</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>56480</t>
+          <t>46134</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>80770</t>
+          <t>63010</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>149049</t>
+          <t>117880</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>129350</t>
+          <t>103331</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>179931</t>
+          <t>131901</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>61,55%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10116</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5665</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>17590</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,8%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,93%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>15,3%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3933</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1240</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9830</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,82%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11225</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5980</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18683</t>
+          <t>8389</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>15158</t>
+          <t>14078</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9031</t>
+          <t>8900</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24078</t>
+          <t>22437</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -1515,57 +1515,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1632,72 +1632,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>40639</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>34740</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>45198</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>70,92%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>60,63%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>78,88%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>27392</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>21719</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>33704</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>49,31%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>39,1%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>60,67%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>44703</t>
+          <t>26130</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>38099</t>
+          <t>20759</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>49850</t>
+          <t>31929</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>72095</t>
+          <t>66769</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>63232</t>
+          <t>58435</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>80980</t>
+          <t>74758</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,1%</t>
         </is>
       </c>
     </row>
@@ -1745,72 +1745,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>16018</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11638</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>21930</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>27,96%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>20,31%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>38,27%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>27509</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>21252</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>33142</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>49,52%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>38,26%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>59,66%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19079</t>
+          <t>27340</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13902</t>
+          <t>21393</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25679</t>
+          <t>32743</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>46588</t>
+          <t>43359</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37817</t>
+          <t>35495</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55615</t>
+          <t>52071</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,74%</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>641</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>3157</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>642</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>3518</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4728</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -1971,57 +1971,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2088,72 +2088,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>36315</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>21300</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>46108</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>52,02%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>30,51%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>66,04%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>41075</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>33700</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>48181</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>58,95%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>48,36%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>69,14%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>39123</t>
+          <t>42381</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21894</t>
+          <t>34494</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50403</t>
+          <t>50070</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>80197</t>
+          <t>78696</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58418</t>
+          <t>61763</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>92660</t>
+          <t>91205</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>65,02%</t>
         </is>
       </c>
     </row>
@@ -2201,72 +2201,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>31496</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>21874</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>46844</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>45,11%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>31,33%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>67,1%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>24405</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>17835</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>31898</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>35,02%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>25,59%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>45,78%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>34246</t>
+          <t>23636</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22624</t>
+          <t>16228</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51330</t>
+          <t>30697</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>58651</t>
+          <t>55132</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>46118</t>
+          <t>42668</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>82320</t>
+          <t>72899</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>51,97%</t>
         </is>
       </c>
     </row>
@@ -2314,72 +2314,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>6042</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>8,65%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>4203</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1569</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>10320</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>14,81%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>4445</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7137</t>
+          <t>10031</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2521</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12975</t>
+          <t>13192</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -2427,57 +2427,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2544,72 +2544,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>38949</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>36477</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>98,41%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>92,16%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>32877</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>30446</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>33887</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>96,13%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>89,02%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>99,08%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>40097</t>
+          <t>34076</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>37566</t>
+          <t>31338</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35116</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>72974</t>
+          <t>73025</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>70162</t>
+          <t>69489</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>74344</t>
+          <t>74389</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -2657,72 +2657,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>7,84%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>1323</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>3754</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>3,87%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>10,98%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>254</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>4032</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>560</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4757</t>
+          <t>5460</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -2883,57 +2883,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3000,72 +3000,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>23542</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>18396</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>28852</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>49,87%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>38,97%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>61,11%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>15854</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>11312</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>21477</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>35,79%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>25,54%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>48,49%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>27414</t>
+          <t>15988</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21165</t>
+          <t>11614</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>33640</t>
+          <t>21169</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>43268</t>
+          <t>39530</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>35698</t>
+          <t>32421</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>51146</t>
+          <t>47013</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>51,38%</t>
         </is>
       </c>
     </row>
@@ -3113,72 +3113,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>23022</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>17833</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>27911</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>48,77%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>37,77%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>59,12%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>26450</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>21205</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>31203</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>59,72%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>47,88%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>70,45%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>25651</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19803</t>
+          <t>21484</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31894</t>
+          <t>30713</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>52101</t>
+          <t>49233</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>44347</t>
+          <t>41691</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>59847</t>
+          <t>56556</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>61,81%</t>
         </is>
       </c>
     </row>
@@ -3226,72 +3226,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>4058</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>8,6%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>1987</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>535</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>4914</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>4,49%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>11,1%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>556</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2703</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>919</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>6351</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -3339,57 +3339,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3456,72 +3456,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>92707</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>82061</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>102744</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>65,95%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>58,38%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>73,09%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>87614</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>77909</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>96820</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>70,83%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>62,98%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>78,27%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>101392</t>
+          <t>86406</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>85218</t>
+          <t>76760</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>113196</t>
+          <t>94351</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>189006</t>
+          <t>179114</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>171864</t>
+          <t>164866</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>203206</t>
+          <t>192491</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>73,36%</t>
         </is>
       </c>
     </row>
@@ -3569,72 +3569,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>40377</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>30473</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>50248</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>28,72%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>21,68%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>35,75%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>31058</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>23207</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>41121</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>25,11%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>18,76%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>33,24%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>46108</t>
+          <t>30123</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>35308</t>
+          <t>22728</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>61975</t>
+          <t>39344</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>77166</t>
+          <t>70501</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>63425</t>
+          <t>58491</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>95593</t>
+          <t>84202</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>32,09%</t>
         </is>
       </c>
     </row>
@@ -3682,107 +3682,107 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>7486</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>3208</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>14021</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>5,33%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>9,97%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>5024</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>2142</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>10050</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>8,12%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>7544</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>2372</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>15148</t>
+          <t>10518</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
+          <t>4,34%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>8,63%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>12779</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>7677</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>20716</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
           <t>4,87%</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>9,77%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>12568</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>7115</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>20674</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>4,51%</t>
-        </is>
-      </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -3795,57 +3795,57 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3912,72 +3912,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>144557</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>137428</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>149776</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>91,99%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>87,46%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>95,32%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>115985</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>108703</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>120863</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>90,15%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>84,49%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>93,94%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>142153</t>
+          <t>124172</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>135254</t>
+          <t>115560</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>147159</t>
+          <t>129677</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,32 +3987,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>258137</t>
+          <t>268729</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>248827</t>
+          <t>258309</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>265822</t>
+          <t>276171</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,61%</t>
         </is>
       </c>
     </row>
@@ -4025,72 +4025,72 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>12152</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>19290</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>7,73%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>4,52%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>12,28%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>11923</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>7139</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>19065</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>9,27%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>5,55%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>14,82%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>11494</t>
+          <t>12908</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>6546</t>
+          <t>7694</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>18119</t>
+          <t>21557</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4100,32 +4100,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>23418</t>
+          <t>25060</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>15693</t>
+          <t>17627</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>32440</t>
+          <t>35987</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>427</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4153,92 +4153,92 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4398</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>819</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>4100</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
           <t>0,59%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>1247</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>2588</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>4888</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>1268</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>4556</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -4251,57 +4251,57 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4368,72 +4368,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>439023</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>411473</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>463185</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>63,92%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>59,91%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>67,44%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>585</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>394014</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>342979</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>421661</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>60,33%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>52,51%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>64,56%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>466116</t>
+          <t>393640</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>435981</t>
+          <t>374528</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>495052</t>
+          <t>412911</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,32 +4443,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>860130</t>
+          <t>832662</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>796725</t>
+          <t>798965</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>899449</t>
+          <t>863679</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>66,18%</t>
         </is>
       </c>
     </row>
@@ -4481,72 +4481,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>225430</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>201867</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>254502</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>32,82%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>29,39%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>37,05%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>306</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>242566</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>214177</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>294628</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>37,14%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>32,79%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>45,11%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>254087</t>
+          <t>207320</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>224987</t>
+          <t>189683</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>285754</t>
+          <t>227608</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>496653</t>
+          <t>432750</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>457445</t>
+          <t>403133</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>565634</t>
+          <t>466004</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>35,71%</t>
         </is>
       </c>
     </row>
@@ -4594,72 +4594,72 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>22371</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>14389</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>31658</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>4,61%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>16554</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>11175</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>24904</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>3,81%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>24530</t>
+          <t>17249</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>16282</t>
+          <t>11233</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>35530</t>
+          <t>25225</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4669,32 +4669,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>41084</t>
+          <t>39620</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>30492</t>
+          <t>29442</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>54260</t>
+          <t>52502</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -4707,57 +4707,57 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
